--- a/YRIGOYEN 9730/Mayo/YRIGOYEN9730-MAYO.xlsx
+++ b/YRIGOYEN 9730/Mayo/YRIGOYEN9730-MAYO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AFC802-EF81-4513-8984-90E192044A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E99E47-CE33-4CE1-A657-5D66D9AE78BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$128</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="107">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -84,12 +84,6 @@
     <t>ABONOS Y SERVICIOS</t>
   </si>
   <si>
-    <t>Seracarh</t>
-  </si>
-  <si>
-    <t>Fatheryh</t>
-  </si>
-  <si>
     <t>HONORARIOS</t>
   </si>
   <si>
@@ -171,9 +165,6 @@
     <t>GASTOS EXTRAORDINARIOS CON PREVISION:</t>
   </si>
   <si>
-    <t>Suther</t>
-  </si>
-  <si>
     <t xml:space="preserve">Deposito sin identificar </t>
   </si>
   <si>
@@ -214,9 +205,6 @@
   </si>
   <si>
     <t xml:space="preserve">Punitorios mal cobrados </t>
-  </si>
-  <si>
-    <t>VTO 14/05</t>
   </si>
   <si>
     <t>PERÍODO: ABRIL</t>
@@ -313,33 +301,12 @@
     <t xml:space="preserve">Plan de pagos ARCA </t>
   </si>
   <si>
-    <t>Debito 16/04</t>
-  </si>
-  <si>
-    <t>Debito 14/04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relleno y colocacion de tapa de camara -  Agustin Godoy </t>
-  </si>
-  <si>
-    <t>Destapacion italoamericana - Abono</t>
-  </si>
-  <si>
     <t>Metrogas Porteria</t>
   </si>
   <si>
-    <t>CONTRERA PAOLA CONTADORA</t>
-  </si>
-  <si>
     <t>EDESUR Porteria</t>
   </si>
   <si>
-    <t>Entrega de documentacion Sra. Stella Maris</t>
-  </si>
-  <si>
-    <t>Colocacion de tres sombreros de ventilacion e impermeabilizacion</t>
-  </si>
-  <si>
     <t>Arca plan de pagos</t>
   </si>
   <si>
@@ -355,10 +322,31 @@
     <t>CONSTANZA</t>
   </si>
   <si>
-    <t>Transferencia 04/04 sin identificar a nombre de Dan tecnica</t>
-  </si>
-  <si>
     <t>SALDO EN BANCO</t>
+  </si>
+  <si>
+    <t>VTO 20/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUSTAVO PADRON - SR CONTADOR </t>
+  </si>
+  <si>
+    <t>No se debito - se paga este mes</t>
+  </si>
+  <si>
+    <t>Debito 16/05</t>
+  </si>
+  <si>
+    <t>Transferencia 09/05 sin identificar a nombre de Dan tecnica</t>
+  </si>
+  <si>
+    <t>Debito 12/05</t>
+  </si>
+  <si>
+    <t>Debito 27/05</t>
+  </si>
+  <si>
+    <t>Debito 25/05</t>
   </si>
 </sst>
 </file>
@@ -375,7 +363,7 @@
     <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,6 +560,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1052,7 +1048,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1260,132 +1256,33 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1396,9 +1293,102 @@
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1763,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1773,6 +1763,7 @@
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
@@ -1780,7 +1771,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
@@ -1789,7 +1780,7 @@
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" s="73"/>
       <c r="D2" s="73"/>
@@ -1797,19 +1788,19 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="178" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="179"/>
+      <c r="B3" s="182" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="183"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -1817,72 +1808,72 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="187" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="187"/>
+      <c r="B8" s="179" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="179"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="187"/>
-      <c r="C9" s="187"/>
+      <c r="B9" s="179"/>
+      <c r="C9" s="179"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="187"/>
-      <c r="C10" s="187"/>
+      <c r="B10" s="179"/>
+      <c r="C10" s="179"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="186" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="186"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="186"/>
+      <c r="A13" s="178" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="178"/>
+      <c r="C13" s="178"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="178"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="186"/>
-      <c r="B14" s="186"/>
-      <c r="C14" s="186"/>
-      <c r="D14" s="186"/>
-      <c r="E14" s="186"/>
+      <c r="A14" s="178"/>
+      <c r="B14" s="178"/>
+      <c r="C14" s="178"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="178"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="186"/>
-      <c r="B15" s="186"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="186"/>
+      <c r="A15" s="178"/>
+      <c r="B15" s="178"/>
+      <c r="C15" s="178"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="186"/>
-      <c r="B16" s="186"/>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
+      <c r="A16" s="178"/>
+      <c r="B16" s="178"/>
+      <c r="C16" s="178"/>
+      <c r="D16" s="178"/>
+      <c r="E16" s="178"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1900,7 +1891,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
@@ -1909,11 +1900,11 @@
     </row>
     <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="203">
+      <c r="D22" s="164">
         <f>650000+29618</f>
         <v>679618</v>
       </c>
@@ -1923,23 +1914,23 @@
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="147"/>
+      <c r="D23" s="164"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="147"/>
+      <c r="D24" s="164"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="147">
+      <c r="D25" s="164">
         <v>0</v>
       </c>
       <c r="E25" s="5"/>
@@ -1948,78 +1939,78 @@
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="147"/>
+      <c r="D26" s="164"/>
       <c r="E26" s="5"/>
       <c r="G26" s="22"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27" s="59"/>
       <c r="C27" s="59"/>
-      <c r="D27" s="148">
+      <c r="D27" s="201">
         <f>SUM(D22:D26)</f>
         <v>679618</v>
       </c>
-      <c r="E27" s="149"/>
+      <c r="E27" s="147"/>
       <c r="G27" s="22"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="173"/>
+      <c r="D28" s="164"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="147"/>
+      <c r="D29" s="164"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="147"/>
+      <c r="D30" s="164"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="150"/>
+      <c r="D31" s="202"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="150"/>
+      <c r="D32" s="202"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="150"/>
+      <c r="D33" s="202"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="150">
+      <c r="D34" s="202">
         <v>0</v>
       </c>
       <c r="E34" s="5"/>
@@ -2028,20 +2019,20 @@
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="150"/>
+      <c r="D35" s="202"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B36" s="59"/>
       <c r="C36" s="59"/>
-      <c r="D36" s="151">
+      <c r="D36" s="203">
         <f>SUM(D28:D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="149"/>
+      <c r="E36" s="147"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="30" t="s">
@@ -2049,8 +2040,8 @@
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="153">
+      <c r="D37" s="204"/>
+      <c r="E37" s="148">
         <f>D27+D36</f>
         <v>679618</v>
       </c>
@@ -2058,35 +2049,35 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
-      <c r="D38" s="154"/>
-      <c r="E38" s="155"/>
+      <c r="D38" s="205"/>
+      <c r="E38" s="149"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="182" t="s">
+      <c r="A39" s="180" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="183"/>
+      <c r="B39" s="181"/>
       <c r="C39" s="54"/>
-      <c r="D39" s="147">
-        <v>40000</v>
-      </c>
-      <c r="E39" s="156"/>
+      <c r="D39" s="164">
+        <v>28000</v>
+      </c>
+      <c r="E39" s="150"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="183"/>
+      <c r="A40" s="180" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="181"/>
       <c r="C40" s="54"/>
-      <c r="D40" s="217">
+      <c r="D40" s="206">
         <v>107000</v>
       </c>
-      <c r="E40" s="156"/>
-      <c r="H40" s="175"/>
+      <c r="E40" s="150"/>
+      <c r="H40" s="162"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="30" t="s">
@@ -2094,42 +2085,42 @@
       </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="158">
+      <c r="D41" s="207"/>
+      <c r="E41" s="151">
         <f>SUM(D39:D40)</f>
-        <v>147000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
-      <c r="D42" s="159"/>
-      <c r="E42" s="160"/>
+      <c r="D42" s="208"/>
+      <c r="E42" s="152"/>
     </row>
     <row r="43" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="180" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43" s="181"/>
+      <c r="A43" s="176" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="177"/>
       <c r="C43" s="56"/>
-      <c r="D43" s="176">
+      <c r="D43" s="209">
         <v>71883</v>
       </c>
-      <c r="E43" s="161"/>
+      <c r="E43" s="153"/>
     </row>
     <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="180" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="181"/>
+      <c r="A44" s="176" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="177"/>
       <c r="C44" s="56"/>
-      <c r="D44" s="162">
+      <c r="D44" s="210">
         <v>131172</v>
       </c>
-      <c r="E44" s="161"/>
+      <c r="E44" s="153"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="30" t="s">
@@ -2137,8 +2128,8 @@
       </c>
       <c r="B45" s="30"/>
       <c r="C45" s="30"/>
-      <c r="D45" s="157"/>
-      <c r="E45" s="163">
+      <c r="D45" s="207"/>
+      <c r="E45" s="154">
         <f>SUM(D43:D44)</f>
         <v>203055</v>
       </c>
@@ -2147,72 +2138,65 @@
       <c r="A46" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="164"/>
-      <c r="C46" s="164"/>
-      <c r="D46" s="165"/>
-      <c r="E46" s="166"/>
+      <c r="B46" s="155"/>
+      <c r="C46" s="155"/>
+      <c r="D46" s="211"/>
+      <c r="E46" s="156"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C47" s="54"/>
-      <c r="D47" s="37">
-        <v>517074.91</v>
-      </c>
-      <c r="E47" s="204" t="s">
-        <v>96</v>
-      </c>
+      <c r="D47" s="212"/>
+      <c r="E47" s="165"/>
       <c r="G47" s="128"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="54"/>
-      <c r="D48" s="37">
+      <c r="D48" s="212">
         <v>10602.27</v>
       </c>
-      <c r="E48" s="204" t="s">
-        <v>95</v>
+      <c r="E48" s="165" t="s">
+        <v>102</v>
       </c>
       <c r="G48" s="128"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="54"/>
-      <c r="D49" s="37">
+      <c r="D49" s="212">
         <v>75532.289999999994</v>
       </c>
-      <c r="E49" s="204" t="str">
+      <c r="E49" s="165" t="str">
         <f>E48</f>
-        <v>Debito 16/04</v>
-      </c>
-      <c r="G49" s="214">
+        <v>Debito 16/05</v>
+      </c>
+      <c r="G49" s="173">
         <f>D49+D48</f>
         <v>86134.56</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="C50" s="5"/>
-      <c r="D50" s="167">
-        <v>73428.649999999994</v>
-      </c>
-      <c r="E50" s="204" t="str">
-        <f>E49</f>
-        <v>Debito 16/04</v>
-      </c>
+      <c r="D50" s="168"/>
+      <c r="E50" s="165"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="str">
@@ -2220,16 +2204,11 @@
         <v>Sindicatos mes de ABRIL</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C51" s="5"/>
-      <c r="D51" s="167">
-        <v>42505.36</v>
-      </c>
-      <c r="E51" s="205" t="str">
-        <f>E50</f>
-        <v>Debito 16/04</v>
-      </c>
+      <c r="D51" s="168"/>
+      <c r="E51" s="166"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="str">
@@ -2237,618 +2216,596 @@
         <v>Sindicatos mes de ABRIL</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="C52" s="5"/>
-      <c r="D52" s="167">
-        <v>4722.82</v>
-      </c>
-      <c r="E52" s="206" t="str">
-        <f>E50</f>
-        <v>Debito 16/04</v>
-      </c>
+      <c r="D52" s="168"/>
+      <c r="E52" s="167"/>
     </row>
     <row r="53" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="164"/>
-      <c r="C53" s="164"/>
-      <c r="D53" s="168"/>
-      <c r="E53" s="163">
+      <c r="B53" s="155"/>
+      <c r="C53" s="155"/>
+      <c r="D53" s="213"/>
+      <c r="E53" s="154">
         <f>SUM(D47:D52)</f>
-        <v>723866.29999999993</v>
+        <v>86134.56</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B54" s="164"/>
-      <c r="C54" s="164"/>
-      <c r="D54" s="165"/>
-      <c r="E54" s="166"/>
+      <c r="B54" s="155"/>
+      <c r="C54" s="155"/>
+      <c r="D54" s="211"/>
+      <c r="E54" s="156"/>
     </row>
     <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="167">
-        <v>43689.57</v>
-      </c>
-      <c r="E55" s="204" t="s">
-        <v>96</v>
+      <c r="D55" s="168">
+        <v>35225.949999999997</v>
+      </c>
+      <c r="E55" s="165" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="167">
-        <v>35800.769999999997</v>
-      </c>
-      <c r="E56" s="204" t="s">
-        <v>96</v>
+      <c r="D56" s="168">
+        <v>17757.169999999998</v>
+      </c>
+      <c r="E56" s="165" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="167">
-        <v>23006.55</v>
-      </c>
-      <c r="E57" s="204" t="s">
-        <v>96</v>
+      <c r="D57" s="168">
+        <v>25893.02</v>
+      </c>
+      <c r="E57" s="165" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="180" t="s">
-        <v>88</v>
-      </c>
-      <c r="B58" s="181"/>
+      <c r="A58" s="176" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" s="177"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="167">
-        <v>331249.57</v>
-      </c>
-      <c r="E58" s="204" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="180" t="s">
-        <v>88</v>
-      </c>
-      <c r="B59" s="181"/>
-      <c r="C59" s="169"/>
-      <c r="D59" s="208">
-        <v>353484.46</v>
-      </c>
-      <c r="E59" s="204" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="30" t="s">
+      <c r="D58" s="168">
+        <v>338035.95</v>
+      </c>
+      <c r="E58" s="165" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="30" t="s">
         <v>4</v>
       </c>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="214"/>
+      <c r="E59" s="154">
+        <f>SUM(D55:D58)</f>
+        <v>416912.09</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="36"/>
       <c r="B60" s="30"/>
       <c r="C60" s="30"/>
       <c r="D60" s="207"/>
-      <c r="E60" s="163">
-        <f>SUM(D55:D59)</f>
-        <v>787230.92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="36"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="157"/>
-      <c r="E61" s="170"/>
+      <c r="E60" s="158"/>
+    </row>
+    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="176"/>
+      <c r="B61" s="177"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="168"/>
+      <c r="E61" s="169"/>
     </row>
     <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="180" t="s">
-        <v>97</v>
-      </c>
-      <c r="B62" s="181"/>
+      <c r="A62" s="172"/>
+      <c r="B62" s="163"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="209">
-        <v>200000</v>
-      </c>
-      <c r="E62" s="210"/>
+      <c r="D62" s="168"/>
+      <c r="E62" s="169"/>
     </row>
     <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="213" t="s">
-        <v>103</v>
-      </c>
-      <c r="B63" s="177"/>
+      <c r="A63" s="180"/>
+      <c r="B63" s="181"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="209">
-        <v>50000</v>
-      </c>
-      <c r="E63" s="210"/>
+      <c r="D63" s="168"/>
+      <c r="E63" s="170"/>
     </row>
     <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="182" t="s">
-        <v>98</v>
-      </c>
-      <c r="B64" s="183"/>
+      <c r="A64" s="180"/>
+      <c r="B64" s="181"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="209">
-        <v>55000</v>
-      </c>
-      <c r="E64" s="211"/>
+      <c r="D64" s="110"/>
+      <c r="E64" s="170"/>
     </row>
     <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="182" t="s">
-        <v>102</v>
-      </c>
-      <c r="B65" s="183"/>
+      <c r="A65" s="176"/>
+      <c r="B65" s="177"/>
       <c r="C65" s="5"/>
-      <c r="D65" s="110">
-        <v>177300</v>
-      </c>
-      <c r="E65" s="211"/>
-    </row>
-    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="182"/>
-      <c r="B66" s="183"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="110"/>
-      <c r="E66" s="211"/>
-    </row>
-    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="180"/>
-      <c r="B67" s="181"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="110"/>
-      <c r="E67" s="212"/>
-      <c r="I67" s="180"/>
-      <c r="J67" s="181"/>
-    </row>
-    <row r="68" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="30" t="s">
+      <c r="D65" s="110"/>
+      <c r="E65" s="171"/>
+      <c r="I65" s="176"/>
+      <c r="J65" s="177"/>
+    </row>
+    <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="171">
-        <f>SUM(D62:D67)</f>
-        <v>482300</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="36" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="159">
+        <f>SUM(D61:D65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B69" s="69"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="152"/>
-      <c r="E69" s="170"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+      <c r="B67" s="69"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="204"/>
+      <c r="E67" s="158"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="167">
-        <v>33262.550000000003</v>
-      </c>
-      <c r="E70" s="172"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="168">
+        <v>19169.759999999998</v>
+      </c>
+      <c r="E68" s="160"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="157"/>
+      <c r="E69" s="41"/>
+    </row>
+    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="53"/>
+      <c r="C70" s="53"/>
+      <c r="D70" s="113"/>
+      <c r="E70" s="107">
+        <f>SUM(D68:D69)</f>
+        <v>19169.759999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
-      <c r="D71" s="167"/>
-      <c r="E71" s="41"/>
+      <c r="D71" s="106"/>
+      <c r="E71" s="114"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B72" s="53"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="113"/>
-      <c r="E72" s="107">
-        <f>SUM(D70:D71)</f>
-        <v>33262.550000000003</v>
+      <c r="A72" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="115"/>
+      <c r="E72" s="116">
+        <v>884362.6</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="106"/>
-      <c r="E73" s="114"/>
+      <c r="A73" s="1"/>
+      <c r="D73" s="117"/>
+      <c r="E73" s="118"/>
+      <c r="F73" s="45"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="B74" s="31"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="115"/>
-      <c r="E74" s="116"/>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1"/>
+      <c r="A74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" s="10"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="119"/>
+      <c r="E74" s="120">
+        <f>(SUM(E30:E72))</f>
+        <v>2424252.0100000002</v>
+      </c>
+      <c r="F74" s="145"/>
+      <c r="G74" s="45"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D75" s="117"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="45"/>
+      <c r="E75" s="117"/>
     </row>
     <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="119"/>
-      <c r="E76" s="120">
-        <f>(SUM(E30:E74))</f>
-        <v>3056332.7699999996</v>
-      </c>
-      <c r="F76" s="145"/>
-      <c r="G76" s="45"/>
+      <c r="D76" s="117"/>
+      <c r="E76" s="117"/>
+      <c r="H76" s="215"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D77" s="117"/>
-      <c r="E77" s="117"/>
-    </row>
-    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D78" s="117"/>
-      <c r="E78" s="117"/>
+      <c r="A77" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" s="12"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="121"/>
+      <c r="E77" s="122"/>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="176"/>
+      <c r="B78" s="177"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="132"/>
+      <c r="E78" s="108"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B79" s="12"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="121"/>
-      <c r="E79" s="122"/>
-    </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="176"/>
+      <c r="B79" s="177"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="110"/>
+      <c r="E79" s="108"/>
+    </row>
+    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="180"/>
       <c r="B80" s="181"/>
       <c r="C80" s="5"/>
-      <c r="D80" s="132"/>
+      <c r="D80" s="110"/>
       <c r="E80" s="108"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="180"/>
-      <c r="B81" s="181"/>
+      <c r="A81" s="109"/>
+      <c r="B81" s="111"/>
       <c r="C81" s="5"/>
       <c r="D81" s="110"/>
       <c r="E81" s="108"/>
     </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="182"/>
-      <c r="B82" s="183"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="110"/>
-      <c r="E82" s="108"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="109"/>
-      <c r="B83" s="111"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="110"/>
-      <c r="E83" s="108"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="51"/>
-      <c r="B84" s="50"/>
-      <c r="C84" s="50"/>
-      <c r="D84" s="60"/>
-      <c r="E84" s="60">
-        <f>SUM(D80:D83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="51"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="60">
+        <f>SUM(D78:D81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B85" s="31"/>
+      <c r="C85" s="31"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="105"/>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="105"/>
+      <c r="A87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87" s="10"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="70">
+        <f>E82+E85</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="70">
-        <f>E84+E87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A89" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" s="104">
+        <f>E74</f>
+        <v>2424252.0100000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" s="104">
+        <f>E74-E72</f>
+        <v>1539889.4100000001</v>
+      </c>
+    </row>
     <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="103" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B91" s="104">
-        <f>E76</f>
-        <v>3056332.7699999996</v>
+        <f>E87-E85</f>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="103" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B92" s="104">
-        <f>E76-E74</f>
-        <v>3056332.7699999996</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="B93" s="104">
-        <f>E89-E87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="103" t="s">
-        <v>47</v>
-      </c>
-      <c r="B94" s="104">
-        <f>E89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <f>E87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="184"/>
+      <c r="B95" s="184"/>
+      <c r="C95" s="184"/>
+      <c r="D95" s="184"/>
+      <c r="E95" s="184"/>
+    </row>
+    <row r="96" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="184"/>
+      <c r="B96" s="184"/>
+      <c r="C96" s="184"/>
+      <c r="D96" s="184"/>
+      <c r="E96" s="184"/>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="184"/>
       <c r="B97" s="184"/>
       <c r="C97" s="184"/>
       <c r="D97" s="184"/>
       <c r="E97" s="184"/>
     </row>
-    <row r="98" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="184"/>
-      <c r="B98" s="184"/>
-      <c r="C98" s="184"/>
-      <c r="D98" s="184"/>
-      <c r="E98" s="184"/>
-    </row>
-    <row r="99" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="184"/>
-      <c r="B99" s="184"/>
-      <c r="C99" s="184"/>
-      <c r="D99" s="184"/>
-      <c r="E99" s="184"/>
-    </row>
-    <row r="101" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B101" s="129"/>
+    <row r="99" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B99" s="129"/>
+      <c r="C99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="34"/>
+      <c r="B100" s="61">
+        <v>0</v>
+      </c>
+      <c r="C100" s="26"/>
+    </row>
+    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101" s="41">
+        <f>PRORRATEO!F29</f>
+        <v>2375296.62</v>
+      </c>
       <c r="C101" s="24"/>
     </row>
     <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="34"/>
-      <c r="B102" s="61">
-        <v>0</v>
-      </c>
-      <c r="C102" s="26"/>
-    </row>
-    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="25"/>
+      <c r="B102" s="41">
+        <v>0</v>
+      </c>
+      <c r="C102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B103" s="41">
-        <f>PRORRATEO!F29</f>
-        <v>2339468.3800000004</v>
+        <v>46</v>
+      </c>
+      <c r="B103" s="112">
+        <f>B125</f>
+        <v>129843</v>
       </c>
       <c r="C103" s="24"/>
     </row>
     <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="25"/>
-      <c r="B104" s="41">
-        <v>0</v>
-      </c>
+      <c r="A104" s="28"/>
+      <c r="B104" s="49"/>
       <c r="C104" s="24"/>
     </row>
     <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B105" s="112">
-        <f>B127</f>
-        <v>129805.08</v>
-      </c>
+      <c r="A105" s="127" t="s">
+        <v>51</v>
+      </c>
+      <c r="B105" s="49"/>
       <c r="C105" s="24"/>
     </row>
     <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="28"/>
-      <c r="B106" s="49"/>
+      <c r="A106" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106" s="49">
+        <f>-B90</f>
+        <v>-1539889.4100000001</v>
+      </c>
       <c r="C106" s="24"/>
     </row>
     <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="127" t="s">
-        <v>54</v>
-      </c>
-      <c r="B107" s="49"/>
+      <c r="A107" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B107" s="49">
+        <f>-(B91)</f>
+        <v>0</v>
+      </c>
       <c r="C107" s="24"/>
     </row>
     <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B108" s="49">
-        <f>-B92</f>
-        <v>-3056332.7699999996</v>
-      </c>
-      <c r="C108" s="24"/>
-    </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B109" s="49">
-        <f>-(B93)</f>
-        <v>0</v>
-      </c>
-      <c r="C109" s="24"/>
-    </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="33" t="s">
+      <c r="A108" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B110" s="61">
-        <f>SUM(B102:B109)</f>
-        <v>-587059.30999999912</v>
-      </c>
+      <c r="B108" s="61">
+        <f>SUM(B100:B107)</f>
+        <v>965250.21</v>
+      </c>
+      <c r="C108" s="27"/>
+      <c r="D108" s="45"/>
+    </row>
+    <row r="109" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="42"/>
+      <c r="C109" s="27"/>
+      <c r="D109" s="45"/>
+      <c r="E109" s="130"/>
+      <c r="F109" s="131"/>
+    </row>
+    <row r="110" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="43"/>
       <c r="C110" s="27"/>
-      <c r="D110" s="45"/>
-    </row>
-    <row r="111" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111"/>
       <c r="B111" s="42"/>
-      <c r="C111" s="27"/>
-      <c r="D111" s="45"/>
-      <c r="E111" s="130"/>
-      <c r="F111" s="131"/>
-    </row>
-    <row r="112" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="43"/>
-      <c r="C112" s="27"/>
-    </row>
-    <row r="113" spans="1:13" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113"/>
-      <c r="B113" s="42"/>
-      <c r="C113" s="38"/>
-    </row>
-    <row r="114" spans="1:13" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="135" t="s">
-        <v>110</v>
-      </c>
-      <c r="B114" s="136">
-        <v>1222657.33</v>
-      </c>
-      <c r="C114" s="38"/>
-      <c r="D114" s="48"/>
+      <c r="C111" s="38"/>
+    </row>
+    <row r="112" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="135" t="s">
+        <v>98</v>
+      </c>
+      <c r="B112" s="136">
+        <v>635598.02000000095</v>
+      </c>
+      <c r="C112" s="38"/>
+      <c r="D112" s="48"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B113" s="141">
+        <f>-B90</f>
+        <v>-1539889.4100000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B114" s="141">
+        <f>-B91</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="56" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="B115" s="141">
-        <f>-B92</f>
-        <v>-3056332.7699999996</v>
+        <f>B125</f>
+        <v>129843</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="B116" s="141">
-        <f>-B93</f>
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="B116" s="142">
+        <f>PRORRATEO!F29</f>
+        <v>2375296.62</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="B117" s="141">
-        <f>B127</f>
-        <v>129805.08</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="B118" s="142">
-        <f>PRORRATEO!F29</f>
-        <v>2339468.3800000004</v>
+      <c r="A117" s="143" t="s">
+        <v>59</v>
+      </c>
+      <c r="B117" s="144">
+        <v>-2212</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="139" t="s">
+        <v>53</v>
+      </c>
+      <c r="B118" s="140">
+        <f>SUM(B112:C117)</f>
+        <v>1598636.2300000009</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="143" t="s">
-        <v>62</v>
-      </c>
-      <c r="B119" s="144"/>
-    </row>
-    <row r="120" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="139" t="s">
-        <v>56</v>
-      </c>
-      <c r="B120" s="140">
-        <f>SUM(B114:C119)</f>
-        <v>635598.02000000095</v>
-      </c>
-    </row>
+      <c r="A119" s="137"/>
+      <c r="B119" s="137"/>
+    </row>
+    <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="137"/>
-      <c r="B121" s="137"/>
-    </row>
-    <row r="122" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="185" t="s">
-        <v>36</v>
-      </c>
-      <c r="B123" s="185"/>
-      <c r="C123" s="185"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="185"/>
-      <c r="B124" s="185"/>
-      <c r="C124" s="185"/>
-    </row>
-    <row r="125" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="124" t="s">
-        <v>109</v>
-      </c>
-      <c r="B125" s="37">
-        <v>129805.08</v>
-      </c>
-      <c r="C125" s="37">
+      <c r="A121" s="185" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" s="185"/>
+      <c r="C121" s="185"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="185"/>
+      <c r="B122" s="185"/>
+      <c r="C122" s="185"/>
+    </row>
+    <row r="123" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="124" t="s">
+        <v>103</v>
+      </c>
+      <c r="B123" s="37">
+        <v>129843</v>
+      </c>
+      <c r="C123" s="37">
         <v>40000</v>
       </c>
-      <c r="E125" s="145"/>
-    </row>
-    <row r="126" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="124"/>
-      <c r="B126" s="126"/>
-      <c r="C126" s="123"/>
-      <c r="D126" s="145"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="46" t="s">
+      <c r="E123" s="145"/>
+    </row>
+    <row r="124" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="124"/>
+      <c r="B124" s="126"/>
+      <c r="C124" s="123"/>
+      <c r="D124" s="145"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B127" s="125">
-        <f>SUM(B125:B126)</f>
-        <v>129805.08</v>
-      </c>
-      <c r="C127" s="47"/>
+      <c r="B125" s="125">
+        <f>SUM(B123:B124)</f>
+        <v>129843</v>
+      </c>
+      <c r="C125" s="47"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M126" s="8"/>
+    </row>
+    <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="184"/>
+      <c r="B127" s="184"/>
+      <c r="C127" s="184"/>
+      <c r="D127" s="184"/>
+      <c r="E127" s="184"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M128" s="8"/>
-    </row>
-    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="184"/>
+      <c r="B128" s="184"/>
+      <c r="C128" s="184"/>
+      <c r="D128" s="184"/>
+      <c r="E128" s="184"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="184"/>
       <c r="B129" s="184"/>
       <c r="C129" s="184"/>
@@ -2862,24 +2819,20 @@
       <c r="D130" s="184"/>
       <c r="E130" s="184"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="184"/>
-      <c r="B131" s="184"/>
-      <c r="C131" s="184"/>
-      <c r="D131" s="184"/>
-      <c r="E131" s="184"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="184"/>
-      <c r="B132" s="184"/>
-      <c r="C132" s="184"/>
-      <c r="D132" s="184"/>
-      <c r="E132" s="184"/>
-    </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A62:B62"/>
+  <mergeCells count="19">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A127:E130"/>
+    <mergeCell ref="A121:C122"/>
+    <mergeCell ref="A95:E97"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A43:B43"/>
@@ -2887,18 +2840,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A129:E132"/>
-    <mergeCell ref="A123:C124"/>
-    <mergeCell ref="A97:E99"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2935,16 +2876,16 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
+      <c r="K1" s="186"/>
+      <c r="L1" s="186"/>
+      <c r="M1" s="186"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
@@ -2953,10 +2894,10 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="215">
+      <c r="F2" s="174">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
@@ -2964,12 +2905,11 @@
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="134">
-        <f>2290000-F2</f>
-        <v>2203865.44</v>
+        <v>2424251.9840000002</v>
       </c>
       <c r="N2" s="57"/>
       <c r="O2" s="57"/>
@@ -2993,90 +2933,90 @@
       <c r="O3" s="62"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="190" t="s">
+      <c r="A4" s="191" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="190" t="s">
+      <c r="B4" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="190" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="190" t="s">
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="194" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="190" t="s">
+      <c r="E4" s="187" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="190" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="198" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="194" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="194" t="s">
+      <c r="G4" s="191" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="187" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="187" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="194" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="201" t="s">
-        <v>104</v>
+      <c r="K4" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="196" t="s">
+        <v>93</v>
       </c>
       <c r="M4" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="196" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="188" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="N4" s="189" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="198" t="s">
+        <v>40</v>
       </c>
       <c r="R4" s="45"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="192"/>
       <c r="B5" s="192"/>
-      <c r="C5" s="191"/>
+      <c r="C5" s="200"/>
       <c r="D5" s="192"/>
-      <c r="E5" s="195"/>
+      <c r="E5" s="188"/>
       <c r="F5" s="192"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="199"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="200"/>
-      <c r="K5" s="195"/>
-      <c r="L5" s="202"/>
+      <c r="G5" s="200"/>
+      <c r="H5" s="194"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="188"/>
+      <c r="L5" s="197"/>
       <c r="M5" s="63" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 14/05</v>
-      </c>
-      <c r="N5" s="197"/>
-      <c r="O5" s="189"/>
+        <v>VTO 20/06</v>
+      </c>
+      <c r="N5" s="190"/>
+      <c r="O5" s="199"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
         <v>1</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C6" s="66"/>
       <c r="D6" s="75">
         <v>6.69</v>
       </c>
       <c r="E6" s="76">
-        <v>153155.01</v>
+        <v>153201.01</v>
       </c>
       <c r="F6" s="78">
         <f>E6</f>
-        <v>153155.01</v>
+        <v>153201.01</v>
       </c>
       <c r="G6" s="78"/>
       <c r="H6" s="79">
@@ -3092,23 +3032,23 @@
       </c>
       <c r="K6" s="81">
         <f>M$2*D6/100</f>
-        <v>147438.59793600001</v>
-      </c>
-      <c r="L6" s="216">
+        <v>162182.45772960002</v>
+      </c>
+      <c r="L6" s="175">
         <f>F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
       <c r="M6" s="83">
         <f>ROUND(SUM(H6:L6),0) + P6</f>
-        <v>153201.01</v>
+        <v>167945.01</v>
       </c>
       <c r="N6" s="84">
         <f>ROUND(M6*6% + M6,0) + P6</f>
-        <v>162393.01</v>
+        <v>178022.01</v>
       </c>
       <c r="O6" s="85">
         <f>ROUND(M6*3%,0) + M6</f>
-        <v>157797.01</v>
+        <v>172983.01</v>
       </c>
       <c r="P6" s="45">
         <v>0.01</v>
@@ -3120,14 +3060,14 @@
         <v>2</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="75">
         <v>5.88</v>
       </c>
       <c r="E7" s="76">
-        <v>450412.02</v>
+        <v>351308.02</v>
       </c>
       <c r="F7" s="78">
         <v>250000</v>
@@ -3135,34 +3075,34 @@
       <c r="G7" s="78"/>
       <c r="H7" s="79">
         <f t="shared" ref="H7:H23" si="0">E7-F7</f>
-        <v>200412.02000000002</v>
+        <v>101308.02000000002</v>
       </c>
       <c r="I7" s="79">
         <f t="shared" ref="I7:I23" si="1">IF(H7&gt;0,H7*3%,0)</f>
-        <v>6012.3606</v>
+        <v>3039.2406000000005</v>
       </c>
       <c r="J7" s="80">
         <v>0</v>
       </c>
       <c r="K7" s="81">
         <f t="shared" ref="K7:K23" si="2">M$2*D7%</f>
-        <v>129587.28787199999</v>
-      </c>
-      <c r="L7" s="216">
+        <v>142546.01665920002</v>
+      </c>
+      <c r="L7" s="175">
         <f t="shared" ref="L7:L23" si="3">F$2*D7/100</f>
         <v>5064.7121280000001</v>
       </c>
       <c r="M7" s="83">
         <f t="shared" ref="M7:M23" si="4">ROUND(SUM(H7:L7),0) + P7</f>
-        <v>341076.02</v>
+        <v>251958.02</v>
       </c>
       <c r="N7" s="84">
         <f t="shared" ref="N7:N23" si="5">ROUND(M7*6% + M7,0) + P7</f>
-        <v>361541.02</v>
+        <v>267076.02</v>
       </c>
       <c r="O7" s="85">
         <f t="shared" ref="O7:O23" si="6">ROUND(M7*3%,0) + M7</f>
-        <v>351308.02</v>
+        <v>259517.02</v>
       </c>
       <c r="P7" s="45">
         <f>P6+0.01</f>
@@ -3176,23 +3116,22 @@
         <v>3</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="75">
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
-        <v>152240.03</v>
+        <v>152285.03</v>
       </c>
       <c r="F8" s="78">
-        <f t="shared" ref="F7:F23" si="8">E8</f>
-        <v>152240.03</v>
+        <v>152500.03</v>
       </c>
       <c r="G8" s="78"/>
       <c r="H8" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-215</v>
       </c>
       <c r="I8" s="79">
         <f t="shared" si="1"/>
@@ -3203,26 +3142,26 @@
       </c>
       <c r="K8" s="81">
         <f t="shared" si="2"/>
-        <v>146557.05176</v>
-      </c>
-      <c r="L8" s="216">
+        <v>161212.75693600002</v>
+      </c>
+      <c r="L8" s="175">
         <f t="shared" si="3"/>
         <v>5727.9482400000006</v>
       </c>
       <c r="M8" s="83">
         <f t="shared" si="4"/>
-        <v>152285.03</v>
+        <v>166726.03</v>
       </c>
       <c r="N8" s="84">
         <f t="shared" si="5"/>
-        <v>161422.03</v>
+        <v>176730.03</v>
       </c>
       <c r="O8" s="85">
         <f t="shared" si="6"/>
-        <v>156854.03</v>
+        <v>171728.03</v>
       </c>
       <c r="P8" s="45">
-        <f t="shared" ref="P8:P24" si="9">P7+0.01</f>
+        <f t="shared" ref="P8:P24" si="8">P7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
@@ -3232,18 +3171,18 @@
         <v>4</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="75">
         <v>6.73</v>
       </c>
       <c r="E9" s="76">
-        <v>154072.04</v>
+        <v>154117.04</v>
       </c>
       <c r="F9" s="78">
-        <f t="shared" si="8"/>
-        <v>154072.04</v>
+        <f t="shared" ref="F8:F23" si="9">E9</f>
+        <v>154117.04</v>
       </c>
       <c r="G9" s="78"/>
       <c r="H9" s="79">
@@ -3259,26 +3198,26 @@
       </c>
       <c r="K9" s="81">
         <f t="shared" si="2"/>
-        <v>148320.14411199998</v>
-      </c>
-      <c r="L9" s="216">
+        <v>163152.15852320002</v>
+      </c>
+      <c r="L9" s="175">
         <f t="shared" si="3"/>
         <v>5796.855888</v>
       </c>
       <c r="M9" s="83">
         <f t="shared" si="4"/>
-        <v>154117.04</v>
+        <v>168949.04</v>
       </c>
       <c r="N9" s="84">
         <f t="shared" si="5"/>
-        <v>163364.04</v>
+        <v>179086.04</v>
       </c>
       <c r="O9" s="85">
         <f t="shared" si="6"/>
-        <v>158741.04</v>
+        <v>174017.04</v>
       </c>
       <c r="P9" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="R9" s="45"/>
@@ -3289,18 +3228,18 @@
         <v>5</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="75">
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="76">
-        <v>184061.05</v>
+        <v>189639.05</v>
       </c>
       <c r="F10" s="78">
-        <f t="shared" si="8"/>
-        <v>184061.05</v>
+        <f>E10</f>
+        <v>189639.05</v>
       </c>
       <c r="G10" s="78"/>
       <c r="H10" s="79">
@@ -3316,26 +3255,26 @@
       </c>
       <c r="K10" s="81">
         <f t="shared" si="2"/>
-        <v>177190.78137599997</v>
-      </c>
-      <c r="L10" s="216">
+        <v>194909.85951359998</v>
+      </c>
+      <c r="L10" s="175">
         <f t="shared" si="3"/>
         <v>6925.2186239999983</v>
       </c>
       <c r="M10" s="83">
         <f t="shared" si="4"/>
-        <v>184116.05</v>
+        <v>201835.05</v>
       </c>
       <c r="N10" s="84">
         <f t="shared" si="5"/>
-        <v>195163.05</v>
+        <v>213945.05</v>
       </c>
       <c r="O10" s="85">
         <f t="shared" si="6"/>
-        <v>189639.05</v>
+        <v>207890.05</v>
       </c>
       <c r="P10" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="R10" s="45"/>
@@ -3346,18 +3285,18 @@
         <v>6</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="75">
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="76">
-        <v>108285.06</v>
+        <v>108317.06</v>
       </c>
       <c r="F11" s="78">
-        <f t="shared" si="8"/>
-        <v>108285.06</v>
+        <f t="shared" si="9"/>
+        <v>108317.06</v>
       </c>
       <c r="G11" s="78"/>
       <c r="H11" s="79">
@@ -3373,26 +3312,26 @@
       </c>
       <c r="K11" s="81">
         <f t="shared" si="2"/>
-        <v>104242.835312</v>
-      </c>
-      <c r="L11" s="216">
+        <v>114667.11884320001</v>
+      </c>
+      <c r="L11" s="175">
         <f t="shared" si="3"/>
         <v>4074.1646880000003</v>
       </c>
       <c r="M11" s="83">
         <f t="shared" si="4"/>
-        <v>108317.06</v>
+        <v>118741.06</v>
       </c>
       <c r="N11" s="84">
         <f t="shared" si="5"/>
-        <v>114816.06</v>
+        <v>125866.06</v>
       </c>
       <c r="O11" s="85">
         <f t="shared" si="6"/>
-        <v>111567.06</v>
+        <v>122303.06</v>
       </c>
       <c r="P11" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
@@ -3402,50 +3341,50 @@
         <v>7</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="75">
         <v>5.67</v>
       </c>
       <c r="E12" s="76">
-        <v>129805.07</v>
+        <v>263542.07</v>
       </c>
       <c r="F12" s="78"/>
       <c r="G12" s="78"/>
       <c r="H12" s="79">
         <f t="shared" si="0"/>
-        <v>129805.07</v>
+        <v>263542.07</v>
       </c>
       <c r="I12" s="79">
         <f t="shared" si="1"/>
-        <v>3894.1521000000002</v>
+        <v>7906.2620999999999</v>
       </c>
       <c r="J12" s="80">
         <v>0</v>
       </c>
       <c r="K12" s="81">
         <f t="shared" si="2"/>
-        <v>124959.170448</v>
-      </c>
-      <c r="L12" s="216">
+        <v>137455.0874928</v>
+      </c>
+      <c r="L12" s="175">
         <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
       <c r="M12" s="83">
         <f t="shared" si="4"/>
-        <v>263542.07</v>
+        <v>413787.07</v>
       </c>
       <c r="N12" s="84">
         <f t="shared" si="5"/>
-        <v>279355.07</v>
+        <v>438614.07</v>
       </c>
       <c r="O12" s="85">
         <f t="shared" si="6"/>
-        <v>271448.07</v>
+        <v>426201.07</v>
       </c>
       <c r="P12" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -3455,57 +3394,57 @@
         <v>8</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C13" s="67"/>
       <c r="D13" s="75">
         <v>5.67</v>
       </c>
       <c r="E13" s="76">
-        <v>273072.08</v>
+        <v>140975.07999999999</v>
       </c>
       <c r="F13" s="78">
-        <f>160000+106251</f>
-        <v>266251</v>
+        <f>E13</f>
+        <v>140975.07999999999</v>
       </c>
       <c r="G13" s="78"/>
       <c r="H13" s="79">
         <f t="shared" si="0"/>
-        <v>6821.0800000000163</v>
+        <v>0</v>
       </c>
       <c r="I13" s="79">
         <f t="shared" si="1"/>
-        <v>204.63240000000047</v>
+        <v>0</v>
       </c>
       <c r="J13" s="80">
         <v>0</v>
       </c>
       <c r="K13" s="81">
         <f t="shared" si="2"/>
-        <v>124959.170448</v>
-      </c>
-      <c r="L13" s="216">
+        <v>137455.0874928</v>
+      </c>
+      <c r="L13" s="175">
         <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
       <c r="M13" s="83">
         <f t="shared" si="4"/>
-        <v>136869.07999999999</v>
+        <v>142339.07999999999</v>
       </c>
       <c r="N13" s="84">
         <f t="shared" si="5"/>
-        <v>145081.07999999999</v>
+        <v>150879.07999999999</v>
       </c>
       <c r="O13" s="85">
         <f t="shared" si="6"/>
-        <v>140975.07999999999</v>
+        <v>146609.07999999999</v>
       </c>
       <c r="P13" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
       <c r="R13" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3514,18 +3453,18 @@
         <v>9</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="75">
         <v>7.67</v>
       </c>
       <c r="E14" s="76">
-        <v>175592.09</v>
+        <v>175643.09</v>
       </c>
       <c r="F14" s="78">
-        <f t="shared" si="8"/>
-        <v>175592.09</v>
+        <f t="shared" si="9"/>
+        <v>175643.09</v>
       </c>
       <c r="G14" s="78"/>
       <c r="H14" s="79">
@@ -3541,26 +3480,26 @@
       </c>
       <c r="K14" s="81">
         <f t="shared" si="2"/>
-        <v>169036.47924800002</v>
-      </c>
-      <c r="L14" s="216">
+        <v>185940.12717280001</v>
+      </c>
+      <c r="L14" s="175">
         <f t="shared" si="3"/>
         <v>6606.5207519999994</v>
       </c>
       <c r="M14" s="83">
         <f t="shared" si="4"/>
-        <v>175643.09</v>
+        <v>192547.09</v>
       </c>
       <c r="N14" s="84">
         <f t="shared" si="5"/>
-        <v>186182.09</v>
+        <v>204100.09</v>
       </c>
       <c r="O14" s="85">
         <f t="shared" si="6"/>
-        <v>180912.09</v>
+        <v>198323.09</v>
       </c>
       <c r="P14" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
     </row>
@@ -3570,18 +3509,18 @@
         <v>10</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="75">
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="76">
-        <v>112177.1</v>
+        <v>115576.1</v>
       </c>
       <c r="F15" s="78">
-        <f t="shared" si="8"/>
-        <v>112177.1</v>
+        <f t="shared" si="9"/>
+        <v>115576.1</v>
       </c>
       <c r="G15" s="78"/>
       <c r="H15" s="79">
@@ -3597,26 +3536,26 @@
       </c>
       <c r="K15" s="81">
         <f t="shared" si="2"/>
-        <v>107989.40656</v>
-      </c>
-      <c r="L15" s="216">
+        <v>118788.34721600001</v>
+      </c>
+      <c r="L15" s="175">
         <f t="shared" si="3"/>
         <v>4220.5934400000006</v>
       </c>
       <c r="M15" s="83">
         <f t="shared" si="4"/>
-        <v>112210.1</v>
+        <v>123009.1</v>
       </c>
       <c r="N15" s="84">
         <f t="shared" si="5"/>
-        <v>118943.1</v>
+        <v>130390.1</v>
       </c>
       <c r="O15" s="85">
         <f t="shared" si="6"/>
-        <v>115576.1</v>
+        <v>126699.1</v>
       </c>
       <c r="P15" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
@@ -3626,18 +3565,18 @@
         <v>11</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C16" s="67"/>
       <c r="D16" s="75">
         <v>5.63</v>
       </c>
       <c r="E16" s="76">
-        <v>128889.11</v>
+        <v>128927.11</v>
       </c>
       <c r="F16" s="78">
-        <f t="shared" si="8"/>
-        <v>128889.11</v>
+        <f t="shared" si="9"/>
+        <v>128927.11</v>
       </c>
       <c r="G16" s="78"/>
       <c r="H16" s="79">
@@ -3653,26 +3592,26 @@
       </c>
       <c r="K16" s="81">
         <f t="shared" si="2"/>
-        <v>124077.62427199999</v>
-      </c>
-      <c r="L16" s="216">
+        <v>136485.3866992</v>
+      </c>
+      <c r="L16" s="175">
         <f t="shared" si="3"/>
         <v>4849.375728</v>
       </c>
       <c r="M16" s="83">
         <f t="shared" si="4"/>
-        <v>128927.11</v>
+        <v>141335.10999999999</v>
       </c>
       <c r="N16" s="84">
         <f t="shared" si="5"/>
-        <v>136663.10999999999</v>
+        <v>149815.10999999999</v>
       </c>
       <c r="O16" s="85">
         <f t="shared" si="6"/>
-        <v>132795.10999999999</v>
+        <v>145575.10999999999</v>
       </c>
       <c r="P16" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
@@ -3682,18 +3621,18 @@
         <v>12</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C17" s="67"/>
       <c r="D17" s="75">
         <v>5.55</v>
       </c>
       <c r="E17" s="76">
-        <v>127057.12</v>
+        <v>127095.12</v>
       </c>
       <c r="F17" s="78">
-        <f t="shared" si="8"/>
-        <v>127057.12</v>
+        <f t="shared" si="9"/>
+        <v>127095.12</v>
       </c>
       <c r="G17" s="78"/>
       <c r="H17" s="79">
@@ -3709,26 +3648,26 @@
       </c>
       <c r="K17" s="81">
         <f t="shared" si="2"/>
-        <v>122314.53191999999</v>
-      </c>
-      <c r="L17" s="216">
+        <v>134545.98511200002</v>
+      </c>
+      <c r="L17" s="175">
         <f t="shared" si="3"/>
         <v>4780.4680799999996</v>
       </c>
       <c r="M17" s="83">
         <f t="shared" si="4"/>
-        <v>127095.12</v>
+        <v>139326.12</v>
       </c>
       <c r="N17" s="84">
         <f t="shared" si="5"/>
-        <v>134721.12</v>
+        <v>147686.12</v>
       </c>
       <c r="O17" s="85">
         <f t="shared" si="6"/>
-        <v>130908.12</v>
+        <v>143506.12</v>
       </c>
       <c r="P17" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
@@ -3738,18 +3677,18 @@
         <v>13</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C18" s="67"/>
       <c r="D18" s="75">
         <v>11.06</v>
       </c>
       <c r="E18" s="76">
-        <v>253199.13</v>
+        <v>253274.13</v>
       </c>
       <c r="F18" s="78">
-        <f t="shared" si="8"/>
-        <v>253199.13</v>
+        <f t="shared" si="9"/>
+        <v>253274.13</v>
       </c>
       <c r="G18" s="78"/>
       <c r="H18" s="79">
@@ -3765,26 +3704,26 @@
       </c>
       <c r="K18" s="81">
         <f t="shared" si="2"/>
-        <v>243747.51766400001</v>
-      </c>
-      <c r="L18" s="216">
+        <v>268122.26943040005</v>
+      </c>
+      <c r="L18" s="175">
         <f t="shared" si="3"/>
         <v>9526.4823360000009</v>
       </c>
       <c r="M18" s="83">
         <f t="shared" si="4"/>
-        <v>253274.13</v>
+        <v>277649.13</v>
       </c>
       <c r="N18" s="84">
         <f t="shared" si="5"/>
-        <v>268471.13</v>
+        <v>294308.13</v>
       </c>
       <c r="O18" s="85">
         <f t="shared" si="6"/>
-        <v>260872.13</v>
+        <v>285978.13</v>
       </c>
       <c r="P18" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
@@ -3794,18 +3733,18 @@
         <v>14</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C19" s="67"/>
       <c r="D19" s="75">
         <v>3.3</v>
       </c>
       <c r="E19" s="76">
-        <v>75547.14</v>
+        <v>75570.14</v>
       </c>
       <c r="F19" s="78">
-        <f t="shared" si="8"/>
-        <v>75547.14</v>
+        <f t="shared" si="9"/>
+        <v>75570.14</v>
       </c>
       <c r="G19" s="78"/>
       <c r="H19" s="79">
@@ -3821,26 +3760,26 @@
       </c>
       <c r="K19" s="81">
         <f t="shared" si="2"/>
-        <v>72727.559519999995</v>
-      </c>
-      <c r="L19" s="216">
+        <v>80000.315472000017</v>
+      </c>
+      <c r="L19" s="175">
         <f t="shared" si="3"/>
         <v>2842.4404799999993</v>
       </c>
       <c r="M19" s="83">
         <f t="shared" si="4"/>
-        <v>75570.14</v>
+        <v>82843.14</v>
       </c>
       <c r="N19" s="84">
         <f t="shared" si="5"/>
-        <v>80104.14</v>
+        <v>87814.14</v>
       </c>
       <c r="O19" s="85">
         <f t="shared" si="6"/>
-        <v>77837.14</v>
+        <v>85328.14</v>
       </c>
       <c r="P19" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
@@ -3850,18 +3789,18 @@
         <v>15</v>
       </c>
       <c r="B20" s="66" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C20" s="67"/>
       <c r="D20" s="75">
         <v>1.8</v>
       </c>
       <c r="E20" s="76">
-        <v>41207.15</v>
+        <v>41220.15</v>
       </c>
       <c r="F20" s="78">
-        <f t="shared" si="8"/>
-        <v>41207.15</v>
+        <f t="shared" si="9"/>
+        <v>41220.15</v>
       </c>
       <c r="G20" s="78"/>
       <c r="H20" s="79">
@@ -3877,26 +3816,26 @@
       </c>
       <c r="K20" s="81">
         <f t="shared" si="2"/>
-        <v>39669.577920000003</v>
-      </c>
-      <c r="L20" s="216">
+        <v>43636.535712000012</v>
+      </c>
+      <c r="L20" s="175">
         <f t="shared" si="3"/>
         <v>1550.4220800000001</v>
       </c>
       <c r="M20" s="83">
         <f t="shared" si="4"/>
-        <v>41220.15</v>
+        <v>45187.15</v>
       </c>
       <c r="N20" s="84">
         <f t="shared" si="5"/>
-        <v>43693.15</v>
+        <v>47898.15</v>
       </c>
       <c r="O20" s="85">
         <f t="shared" si="6"/>
-        <v>42457.15</v>
+        <v>46543.15</v>
       </c>
       <c r="P20" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
@@ -3906,50 +3845,53 @@
         <v>16</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C21" s="66"/>
       <c r="D21" s="75">
         <v>3.22</v>
       </c>
       <c r="E21" s="76">
-        <v>73717.16</v>
-      </c>
-      <c r="F21" s="78"/>
+        <v>149667.16</v>
+      </c>
+      <c r="F21" s="78">
+        <f>73738.16+75929</f>
+        <v>149667.16</v>
+      </c>
       <c r="G21" s="78"/>
       <c r="H21" s="79">
         <f t="shared" si="0"/>
-        <v>73717.16</v>
+        <v>0</v>
       </c>
       <c r="I21" s="79">
         <f t="shared" si="1"/>
-        <v>2211.5147999999999</v>
+        <v>0</v>
       </c>
       <c r="J21" s="80">
         <v>0</v>
       </c>
       <c r="K21" s="81">
         <f t="shared" si="2"/>
-        <v>70964.467168000003</v>
-      </c>
-      <c r="L21" s="216">
+        <v>78060.9138848</v>
+      </c>
+      <c r="L21" s="175">
         <f t="shared" si="3"/>
         <v>2773.5328319999999</v>
       </c>
       <c r="M21" s="83">
         <f t="shared" si="4"/>
-        <v>149667.16</v>
+        <v>80834.16</v>
       </c>
       <c r="N21" s="84">
         <f t="shared" si="5"/>
-        <v>158647.16</v>
+        <v>85684.160000000003</v>
       </c>
       <c r="O21" s="85">
         <f t="shared" si="6"/>
-        <v>154157.16</v>
+        <v>83259.16</v>
       </c>
       <c r="P21" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
       <c r="R21" s="44"/>
@@ -3960,18 +3902,18 @@
         <v>17</v>
       </c>
       <c r="B22" s="66" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C22" s="67"/>
       <c r="D22" s="75">
         <v>2.61</v>
       </c>
       <c r="E22" s="77">
-        <v>59751.17</v>
+        <v>61562.17</v>
       </c>
       <c r="F22" s="78">
         <f>E22</f>
-        <v>59751.17</v>
+        <v>61562.17</v>
       </c>
       <c r="G22" s="78"/>
       <c r="H22" s="79">
@@ -3987,26 +3929,26 @@
       </c>
       <c r="K22" s="81">
         <f t="shared" si="2"/>
-        <v>57520.887983999994</v>
-      </c>
-      <c r="L22" s="216">
+        <v>63272.976782400001</v>
+      </c>
+      <c r="L22" s="175">
         <f t="shared" si="3"/>
         <v>2248.1120159999996</v>
       </c>
       <c r="M22" s="83">
         <f t="shared" si="4"/>
-        <v>59769.17</v>
+        <v>65521.17</v>
       </c>
       <c r="N22" s="84">
         <f t="shared" si="5"/>
-        <v>63355.17</v>
+        <v>69452.17</v>
       </c>
       <c r="O22" s="85">
         <f t="shared" si="6"/>
-        <v>61562.17</v>
+        <v>67487.17</v>
       </c>
       <c r="P22" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
@@ -4016,18 +3958,18 @@
         <v>18</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C23" s="133"/>
       <c r="D23" s="75">
         <v>4.28</v>
       </c>
       <c r="E23" s="76">
-        <v>97984.18</v>
+        <v>98012.18</v>
       </c>
       <c r="F23" s="78">
-        <f t="shared" si="8"/>
-        <v>97984.18</v>
+        <f t="shared" si="9"/>
+        <v>98012.18</v>
       </c>
       <c r="G23" s="78"/>
       <c r="H23" s="79">
@@ -4043,26 +3985,26 @@
       </c>
       <c r="K23" s="81">
         <f t="shared" si="2"/>
-        <v>94325.440832000008</v>
-      </c>
-      <c r="L23" s="216">
+        <v>103757.98491520002</v>
+      </c>
+      <c r="L23" s="175">
         <f t="shared" si="3"/>
         <v>3686.5591680000002</v>
       </c>
       <c r="M23" s="83">
         <f t="shared" si="4"/>
-        <v>98012.18</v>
+        <v>107445.18</v>
       </c>
       <c r="N23" s="84">
         <f t="shared" si="5"/>
-        <v>103893.18</v>
+        <v>113892.18</v>
       </c>
       <c r="O23" s="85">
         <f t="shared" si="6"/>
-        <v>100952.18</v>
+        <v>110668.18</v>
       </c>
       <c r="P23" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="R23" s="146"/>
@@ -4073,7 +4015,7 @@
       <c r="C24" s="67"/>
       <c r="D24" s="75"/>
       <c r="E24" s="76"/>
-      <c r="F24" s="174"/>
+      <c r="F24" s="161"/>
       <c r="G24" s="78"/>
       <c r="H24" s="79"/>
       <c r="I24" s="79"/>
@@ -4084,7 +4026,7 @@
       <c r="N24" s="84"/>
       <c r="O24" s="85"/>
       <c r="P24" s="45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
@@ -4170,11 +4112,11 @@
       </c>
       <c r="E29" s="55">
         <f>SUM(E6:E28)</f>
-        <v>2750223.7100000009</v>
+        <v>2739931.7100000009</v>
       </c>
       <c r="F29" s="64">
         <f>SUM(F6:F28)</f>
-        <v>2339468.3800000004</v>
+        <v>2375296.62</v>
       </c>
       <c r="G29" s="55">
         <f t="shared" ref="G29:N29" si="10">SUM(G6:G28)</f>
@@ -4182,11 +4124,11 @@
       </c>
       <c r="H29" s="64">
         <f>SUM(H6:H28)</f>
-        <v>410755.33000000007</v>
+        <v>364635.09</v>
       </c>
       <c r="I29" s="64">
         <f t="shared" si="10"/>
-        <v>12322.659899999999</v>
+        <v>10945.502700000001</v>
       </c>
       <c r="J29" s="64">
         <f t="shared" si="10"/>
@@ -4194,7 +4136,7 @@
       </c>
       <c r="K29" s="138">
         <f t="shared" si="10"/>
-        <v>2205628.532352</v>
+        <v>2426191.3855872005</v>
       </c>
       <c r="L29" s="64">
         <f t="shared" si="10"/>
@@ -4202,15 +4144,15 @@
       </c>
       <c r="M29" s="101">
         <f>SUM(M6:M23)</f>
-        <v>2714911.7100000009</v>
+        <v>2887977.7100000009</v>
       </c>
       <c r="N29" s="101">
         <f t="shared" si="10"/>
-        <v>2877808.7100000009</v>
+        <v>3061258.7100000009</v>
       </c>
       <c r="O29" s="101">
         <f>SUM(O6:O28)</f>
-        <v>2796358.7100000009</v>
+        <v>2974615.7100000009</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4307,6 +4249,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="E4:E5"/>
@@ -4316,13 +4265,6 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/YRIGOYEN 9730/Mayo/YRIGOYEN9730-MAYO.xlsx
+++ b/YRIGOYEN 9730/Mayo/YRIGOYEN9730-MAYO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E99E47-CE33-4CE1-A657-5D66D9AE78BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F108F94-5793-47DF-8AA0-F0DDBBA577C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="108">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Debito 25/05</t>
+  </si>
+  <si>
+    <t>DAN TECNICA</t>
   </si>
 </sst>
 </file>
@@ -1293,81 +1296,6 @@
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1389,6 +1317,81 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1788,12 +1791,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="182" t="s">
+      <c r="B3" s="191" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="183"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="192"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -1831,49 +1834,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="179" t="s">
+      <c r="B8" s="200" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="179"/>
+      <c r="C8" s="200"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="179"/>
-      <c r="C9" s="179"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="179"/>
-      <c r="C10" s="179"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="178" t="s">
+      <c r="A13" s="199" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="178"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="178"/>
-      <c r="E13" s="178"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199"/>
+      <c r="E13" s="199"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="178"/>
-      <c r="B14" s="178"/>
-      <c r="C14" s="178"/>
-      <c r="D14" s="178"/>
-      <c r="E14" s="178"/>
+      <c r="A14" s="199"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
+      <c r="E14" s="199"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="178"/>
-      <c r="B15" s="178"/>
-      <c r="C15" s="178"/>
-      <c r="D15" s="178"/>
-      <c r="E15" s="178"/>
+      <c r="A15" s="199"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="199"/>
+      <c r="E15" s="199"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="178"/>
-      <c r="B16" s="178"/>
-      <c r="C16" s="178"/>
-      <c r="D16" s="178"/>
-      <c r="E16" s="178"/>
+      <c r="A16" s="199"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="199"/>
+      <c r="E16" s="199"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1949,7 +1952,7 @@
       </c>
       <c r="B27" s="59"/>
       <c r="C27" s="59"/>
-      <c r="D27" s="201">
+      <c r="D27" s="176">
         <f>SUM(D22:D26)</f>
         <v>679618</v>
       </c>
@@ -1983,7 +1986,7 @@
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="202"/>
+      <c r="D31" s="177"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1992,7 +1995,7 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="202"/>
+      <c r="D32" s="177"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2001,7 +2004,7 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="202"/>
+      <c r="D33" s="177"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2010,7 +2013,7 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="202">
+      <c r="D34" s="177">
         <v>0</v>
       </c>
       <c r="E34" s="5"/>
@@ -2019,7 +2022,7 @@
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="202"/>
+      <c r="D35" s="177"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2028,7 +2031,7 @@
       </c>
       <c r="B36" s="59"/>
       <c r="C36" s="59"/>
-      <c r="D36" s="203">
+      <c r="D36" s="178">
         <f>SUM(D28:D35)</f>
         <v>0</v>
       </c>
@@ -2040,7 +2043,7 @@
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
-      <c r="D37" s="204"/>
+      <c r="D37" s="179"/>
       <c r="E37" s="148">
         <f>D27+D36</f>
         <v>679618</v>
@@ -2053,14 +2056,14 @@
       </c>
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
-      <c r="D38" s="205"/>
+      <c r="D38" s="180"/>
       <c r="E38" s="149"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="180" t="s">
+      <c r="A39" s="195" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="181"/>
+      <c r="B39" s="196"/>
       <c r="C39" s="54"/>
       <c r="D39" s="164">
         <v>28000</v>
@@ -2068,12 +2071,12 @@
       <c r="E39" s="150"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="180" t="s">
+      <c r="A40" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="B40" s="181"/>
+      <c r="B40" s="196"/>
       <c r="C40" s="54"/>
-      <c r="D40" s="206">
+      <c r="D40" s="181">
         <v>107000</v>
       </c>
       <c r="E40" s="150"/>
@@ -2085,7 +2088,7 @@
       </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
-      <c r="D41" s="207"/>
+      <c r="D41" s="182"/>
       <c r="E41" s="151">
         <f>SUM(D39:D40)</f>
         <v>135000</v>
@@ -2097,27 +2100,27 @@
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
-      <c r="D42" s="208"/>
+      <c r="D42" s="183"/>
       <c r="E42" s="152"/>
     </row>
     <row r="43" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="176" t="s">
+      <c r="A43" s="193" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="177"/>
+      <c r="B43" s="194"/>
       <c r="C43" s="56"/>
-      <c r="D43" s="209">
+      <c r="D43" s="184">
         <v>71883</v>
       </c>
       <c r="E43" s="153"/>
     </row>
     <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="176" t="s">
+      <c r="A44" s="193" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="177"/>
+      <c r="B44" s="194"/>
       <c r="C44" s="56"/>
-      <c r="D44" s="210">
+      <c r="D44" s="185">
         <v>131172</v>
       </c>
       <c r="E44" s="153"/>
@@ -2128,7 +2131,7 @@
       </c>
       <c r="B45" s="30"/>
       <c r="C45" s="30"/>
-      <c r="D45" s="207"/>
+      <c r="D45" s="182"/>
       <c r="E45" s="154">
         <f>SUM(D43:D44)</f>
         <v>203055</v>
@@ -2140,7 +2143,7 @@
       </c>
       <c r="B46" s="155"/>
       <c r="C46" s="155"/>
-      <c r="D46" s="211"/>
+      <c r="D46" s="186"/>
       <c r="E46" s="156"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -2151,7 +2154,7 @@
         <v>101</v>
       </c>
       <c r="C47" s="54"/>
-      <c r="D47" s="212"/>
+      <c r="D47" s="187"/>
       <c r="E47" s="165"/>
       <c r="G47" s="128"/>
     </row>
@@ -2161,7 +2164,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="54"/>
-      <c r="D48" s="212">
+      <c r="D48" s="187">
         <v>10602.27</v>
       </c>
       <c r="E48" s="165" t="s">
@@ -2175,7 +2178,7 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="54"/>
-      <c r="D49" s="212">
+      <c r="D49" s="187">
         <v>75532.289999999994</v>
       </c>
       <c r="E49" s="165" t="str">
@@ -2228,7 +2231,7 @@
       </c>
       <c r="B53" s="155"/>
       <c r="C53" s="155"/>
-      <c r="D53" s="213"/>
+      <c r="D53" s="188"/>
       <c r="E53" s="154">
         <f>SUM(D47:D52)</f>
         <v>86134.56</v>
@@ -2240,7 +2243,7 @@
       </c>
       <c r="B54" s="155"/>
       <c r="C54" s="155"/>
-      <c r="D54" s="211"/>
+      <c r="D54" s="186"/>
       <c r="E54" s="156"/>
     </row>
     <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2283,10 +2286,10 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="176" t="s">
+      <c r="A58" s="193" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="177"/>
+      <c r="B58" s="194"/>
       <c r="C58" s="5"/>
       <c r="D58" s="168">
         <v>338035.95</v>
@@ -2301,7 +2304,7 @@
       </c>
       <c r="B59" s="30"/>
       <c r="C59" s="30"/>
-      <c r="D59" s="214"/>
+      <c r="D59" s="189"/>
       <c r="E59" s="154">
         <f>SUM(D55:D58)</f>
         <v>416912.09</v>
@@ -2311,12 +2314,12 @@
       <c r="A60" s="36"/>
       <c r="B60" s="30"/>
       <c r="C60" s="30"/>
-      <c r="D60" s="207"/>
+      <c r="D60" s="182"/>
       <c r="E60" s="158"/>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="176"/>
-      <c r="B61" s="177"/>
+      <c r="A61" s="193"/>
+      <c r="B61" s="194"/>
       <c r="C61" s="5"/>
       <c r="D61" s="168"/>
       <c r="E61" s="169"/>
@@ -2329,27 +2332,27 @@
       <c r="E62" s="169"/>
     </row>
     <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="180"/>
-      <c r="B63" s="181"/>
+      <c r="A63" s="195"/>
+      <c r="B63" s="196"/>
       <c r="C63" s="5"/>
       <c r="D63" s="168"/>
       <c r="E63" s="170"/>
     </row>
     <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="180"/>
-      <c r="B64" s="181"/>
+      <c r="A64" s="195"/>
+      <c r="B64" s="196"/>
       <c r="C64" s="5"/>
       <c r="D64" s="110"/>
       <c r="E64" s="170"/>
     </row>
     <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="176"/>
-      <c r="B65" s="177"/>
+      <c r="A65" s="193"/>
+      <c r="B65" s="194"/>
       <c r="C65" s="5"/>
       <c r="D65" s="110"/>
       <c r="E65" s="171"/>
-      <c r="I65" s="176"/>
-      <c r="J65" s="177"/>
+      <c r="I65" s="193"/>
+      <c r="J65" s="194"/>
     </row>
     <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="30" t="s">
@@ -2369,7 +2372,7 @@
       </c>
       <c r="B67" s="69"/>
       <c r="C67" s="30"/>
-      <c r="D67" s="204"/>
+      <c r="D67" s="179"/>
       <c r="E67" s="158"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2447,7 +2450,7 @@
     <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D76" s="117"/>
       <c r="E76" s="117"/>
-      <c r="H76" s="215"/>
+      <c r="H76" s="190"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
@@ -2459,22 +2462,22 @@
       <c r="E77" s="122"/>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="176"/>
-      <c r="B78" s="177"/>
+      <c r="A78" s="193"/>
+      <c r="B78" s="194"/>
       <c r="C78" s="5"/>
       <c r="D78" s="132"/>
       <c r="E78" s="108"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="176"/>
-      <c r="B79" s="177"/>
+      <c r="A79" s="193"/>
+      <c r="B79" s="194"/>
       <c r="C79" s="5"/>
       <c r="D79" s="110"/>
       <c r="E79" s="108"/>
     </row>
     <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="180"/>
-      <c r="B80" s="181"/>
+      <c r="A80" s="195"/>
+      <c r="B80" s="196"/>
       <c r="C80" s="5"/>
       <c r="D80" s="110"/>
       <c r="E80" s="108"/>
@@ -2560,25 +2563,25 @@
     <row r="93" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="184"/>
-      <c r="B95" s="184"/>
-      <c r="C95" s="184"/>
-      <c r="D95" s="184"/>
-      <c r="E95" s="184"/>
+      <c r="A95" s="197"/>
+      <c r="B95" s="197"/>
+      <c r="C95" s="197"/>
+      <c r="D95" s="197"/>
+      <c r="E95" s="197"/>
     </row>
     <row r="96" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="184"/>
-      <c r="B96" s="184"/>
-      <c r="C96" s="184"/>
-      <c r="D96" s="184"/>
-      <c r="E96" s="184"/>
+      <c r="A96" s="197"/>
+      <c r="B96" s="197"/>
+      <c r="C96" s="197"/>
+      <c r="D96" s="197"/>
+      <c r="E96" s="197"/>
     </row>
     <row r="97" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="184"/>
-      <c r="B97" s="184"/>
-      <c r="C97" s="184"/>
-      <c r="D97" s="184"/>
-      <c r="E97" s="184"/>
+      <c r="A97" s="197"/>
+      <c r="B97" s="197"/>
+      <c r="C97" s="197"/>
+      <c r="D97" s="197"/>
+      <c r="E97" s="197"/>
     </row>
     <row r="99" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="23" t="s">
@@ -2749,16 +2752,16 @@
     </row>
     <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="185" t="s">
+      <c r="A121" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="B121" s="185"/>
-      <c r="C121" s="185"/>
+      <c r="B121" s="198"/>
+      <c r="C121" s="198"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="185"/>
-      <c r="B122" s="185"/>
-      <c r="C122" s="185"/>
+      <c r="A122" s="198"/>
+      <c r="B122" s="198"/>
+      <c r="C122" s="198"/>
     </row>
     <row r="123" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="124" t="s">
@@ -2792,35 +2795,38 @@
       <c r="M126" s="8"/>
     </row>
     <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="184"/>
-      <c r="B127" s="184"/>
-      <c r="C127" s="184"/>
-      <c r="D127" s="184"/>
-      <c r="E127" s="184"/>
+      <c r="A127" s="197"/>
+      <c r="B127" s="197"/>
+      <c r="C127" s="197"/>
+      <c r="D127" s="197"/>
+      <c r="E127" s="197"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="184"/>
-      <c r="B128" s="184"/>
-      <c r="C128" s="184"/>
-      <c r="D128" s="184"/>
-      <c r="E128" s="184"/>
+      <c r="A128" s="197"/>
+      <c r="B128" s="197"/>
+      <c r="C128" s="197"/>
+      <c r="D128" s="197"/>
+      <c r="E128" s="197"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="184"/>
-      <c r="B129" s="184"/>
-      <c r="C129" s="184"/>
-      <c r="D129" s="184"/>
-      <c r="E129" s="184"/>
+      <c r="A129" s="197"/>
+      <c r="B129" s="197"/>
+      <c r="C129" s="197"/>
+      <c r="D129" s="197"/>
+      <c r="E129" s="197"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="184"/>
-      <c r="B130" s="184"/>
-      <c r="C130" s="184"/>
-      <c r="D130" s="184"/>
-      <c r="E130" s="184"/>
+      <c r="A130" s="197"/>
+      <c r="B130" s="197"/>
+      <c r="C130" s="197"/>
+      <c r="D130" s="197"/>
+      <c r="E130" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="I65:J65"/>
     <mergeCell ref="A63:B63"/>
@@ -2837,9 +2843,6 @@
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2876,16 +2879,16 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
-      <c r="J1" s="186"/>
-      <c r="K1" s="186"/>
-      <c r="L1" s="186"/>
-      <c r="M1" s="186"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
+      <c r="M1" s="206"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
@@ -2933,72 +2936,72 @@
       <c r="O3" s="62"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="191" t="s">
+      <c r="A4" s="203" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="191" t="s">
+      <c r="B4" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="191" t="s">
+      <c r="C4" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="191" t="s">
+      <c r="D4" s="203" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="187" t="s">
+      <c r="E4" s="207" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="191" t="s">
+      <c r="F4" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="191" t="s">
+      <c r="G4" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="193" t="s">
+      <c r="H4" s="211" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="187" t="s">
+      <c r="I4" s="207" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="187" t="s">
+      <c r="J4" s="207" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="187" t="s">
+      <c r="K4" s="207" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="196" t="s">
+      <c r="L4" s="214" t="s">
         <v>93</v>
       </c>
       <c r="M4" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="189" t="s">
+      <c r="N4" s="209" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="198" t="s">
+      <c r="O4" s="201" t="s">
         <v>40</v>
       </c>
       <c r="R4" s="45"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="192"/>
-      <c r="B5" s="192"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="200"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="197"/>
+      <c r="A5" s="205"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="204"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="213"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="215"/>
       <c r="M5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 20/06</v>
       </c>
-      <c r="N5" s="190"/>
-      <c r="O5" s="199"/>
+      <c r="N5" s="210"/>
+      <c r="O5" s="202"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
@@ -3181,7 +3184,7 @@
         <v>154117.04</v>
       </c>
       <c r="F9" s="78">
-        <f t="shared" ref="F8:F23" si="9">E9</f>
+        <f t="shared" ref="F9:F23" si="9">E9</f>
         <v>154117.04</v>
       </c>
       <c r="G9" s="78"/>
@@ -3386,6 +3389,9 @@
       <c r="P12" s="45">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4161,101 +4167,94 @@
     </row>
     <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="184" t="str">
+      <c r="B32" s="197" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="184"/>
-      <c r="D32" s="184"/>
-      <c r="E32" s="184"/>
-      <c r="F32" s="184"/>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="184"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="184"/>
-      <c r="L32" s="184"/>
-      <c r="M32" s="184"/>
+      <c r="C32" s="197"/>
+      <c r="D32" s="197"/>
+      <c r="E32" s="197"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="197"/>
+      <c r="L32" s="197"/>
+      <c r="M32" s="197"/>
     </row>
     <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="184"/>
-      <c r="C33" s="184"/>
-      <c r="D33" s="184"/>
-      <c r="E33" s="184"/>
-      <c r="F33" s="184"/>
-      <c r="G33" s="184"/>
-      <c r="H33" s="184"/>
-      <c r="I33" s="184"/>
-      <c r="J33" s="184"/>
-      <c r="K33" s="184"/>
-      <c r="L33" s="184"/>
-      <c r="M33" s="184"/>
+      <c r="B33" s="197"/>
+      <c r="C33" s="197"/>
+      <c r="D33" s="197"/>
+      <c r="E33" s="197"/>
+      <c r="F33" s="197"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="197"/>
+      <c r="I33" s="197"/>
+      <c r="J33" s="197"/>
+      <c r="K33" s="197"/>
+      <c r="L33" s="197"/>
+      <c r="M33" s="197"/>
     </row>
     <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="184"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="184"/>
-      <c r="H34" s="184"/>
-      <c r="I34" s="184"/>
-      <c r="J34" s="184"/>
-      <c r="K34" s="184"/>
-      <c r="L34" s="184"/>
-      <c r="M34" s="184"/>
+      <c r="B34" s="197"/>
+      <c r="C34" s="197"/>
+      <c r="D34" s="197"/>
+      <c r="E34" s="197"/>
+      <c r="F34" s="197"/>
+      <c r="G34" s="197"/>
+      <c r="H34" s="197"/>
+      <c r="I34" s="197"/>
+      <c r="J34" s="197"/>
+      <c r="K34" s="197"/>
+      <c r="L34" s="197"/>
+      <c r="M34" s="197"/>
     </row>
     <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="184"/>
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="184"/>
-      <c r="K35" s="184"/>
-      <c r="L35" s="184"/>
-      <c r="M35" s="184"/>
+      <c r="B35" s="197"/>
+      <c r="C35" s="197"/>
+      <c r="D35" s="197"/>
+      <c r="E35" s="197"/>
+      <c r="F35" s="197"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="197"/>
+      <c r="I35" s="197"/>
+      <c r="J35" s="197"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="197"/>
+      <c r="M35" s="197"/>
     </row>
     <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-      <c r="M36" s="184"/>
+      <c r="B36" s="197"/>
+      <c r="C36" s="197"/>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="197"/>
+      <c r="H36" s="197"/>
+      <c r="I36" s="197"/>
+      <c r="J36" s="197"/>
+      <c r="K36" s="197"/>
+      <c r="L36" s="197"/>
+      <c r="M36" s="197"/>
     </row>
     <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="184"/>
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="184"/>
-      <c r="M37" s="184"/>
+      <c r="B37" s="197"/>
+      <c r="C37" s="197"/>
+      <c r="D37" s="197"/>
+      <c r="E37" s="197"/>
+      <c r="F37" s="197"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="197"/>
+      <c r="I37" s="197"/>
+      <c r="J37" s="197"/>
+      <c r="K37" s="197"/>
+      <c r="L37" s="197"/>
+      <c r="M37" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="E4:E5"/>
@@ -4265,6 +4264,13 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
